--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/todos.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/todos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M176"/>
+  <dimension ref="A1:M250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>29497.97</v>
+        <v>29308.99</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4328.97</v>
+        <v>4310.32</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12947.67</v>
+        <v>12760.36</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5791.89</v>
+        <v>5667.28</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5605.05</v>
+        <v>5474.63</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>20047.08</v>
+        <v>19407.85</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>673.88</v>
+        <v>660.59</v>
       </c>
     </row>
     <row r="9">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8476.84</v>
+        <v>8323.120000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1057417-10699-CM26</t>
+          <t>1057417-10664-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>41430.64</v>
+        <v>34533.22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057417-10698-CM26</t>
+          <t>1057417-10665-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>65683.16</v>
+        <v>26393.09</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1057417-10664-CM26</t>
+          <t>1057417-10698-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>35483.34</v>
+        <v>63924.39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1057417-10665-CM26</t>
+          <t>1057417-10699-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>27119.25</v>
+        <v>40321.27</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>28088.19</v>
+        <v>28169.96</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>37692.53</v>
+        <v>37849.18</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>45917.56</v>
+        <v>46307.26</v>
       </c>
     </row>
     <row r="17">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3452.55</v>
+        <v>3446.78</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1255790-68-CM26</t>
+          <t>1671-56-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,32 +1510,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>65.589.950-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R y R LIMITADA</t>
+          <t>INVERSIONES Y TRANSPORTES SAYEN SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>76.438.029-0</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>19084.82</v>
+        <v>11699.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1671-56-CM26</t>
+          <t>2069-3343-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1571,32 +1571,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>INVERSIONES Y TRANSPORTES SAYEN SPA</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.438.029-0</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>11556.92</v>
+        <v>611308.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2069-3343-CM26</t>
+          <t>5441-182-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1632,17 +1632,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>603876.53</v>
+        <v>448.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5441-182-CM26</t>
+          <t>1255790-68-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1693,17 +1693,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>65.589.950-2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>AUTOMOTRIZ R y R LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>443.19</v>
+        <v>19319.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3654-93-CM26</t>
+          <t>745-10-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.101.034-6</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TRAVEL RENT A CAR LIMITADA</t>
+          <t>SOCIEDAD DE TRANSPORTE JIMÉNEZ HERMANOS LTDA.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.854.171-8</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>278.43</v>
+        <v>5642.77</v>
       </c>
     </row>
     <row r="23">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>33732.56</v>
+        <v>34181.63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>745-10-CM26</t>
+          <t>3654-93-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.101.034-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE TRANSPORTE JIMÉNEZ HERMANOS LTDA.</t>
+          <t>TRAVEL RENT A CAR LIMITADA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>77.854.171-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5568.63</v>
+        <v>282.14</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>45105.94</v>
+        <v>45694.56</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>15522.32</v>
+        <v>15904.33</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>111.37</v>
+        <v>113.48</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>34790.04</v>
+        <v>35448.02</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3508.24</v>
+        <v>3519.28</v>
       </c>
     </row>
     <row r="30">
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>202.19</v>
+        <v>202.82</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4766-3470-CM26</t>
+          <t>1161266-265-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2308,27 +2308,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>69.141.800-6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SERVICIOS LOGÍSTICOS  Y TRANSPORTES VIÑA DEL MAR SPA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.345.484-3</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>11109.43</v>
+        <v>25721.89</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1161266-265-CM26</t>
+          <t>4766-3470-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,27 +2369,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.141.800-6</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TUCAPEL</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>SERVICIOS LOGÍSTICOS  Y TRANSPORTES VIÑA DEL MAR SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.345.484-3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>25615.72</v>
+        <v>11155.47</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1213.96</v>
+        <v>1216.48</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>6415.07</v>
+        <v>6387.51</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>16821.93</v>
+        <v>16721.11</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>10694.74</v>
+        <v>10630.64</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1632.06</v>
+        <v>1622.28</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>8578.07</v>
+        <v>8461.450000000001</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>10549.64</v>
+        <v>10406.21</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>22658.99</v>
+        <v>22350.92</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>17499.26</v>
+        <v>17593.49</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>22536.93</v>
+        <v>22788.97</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6439.12</v>
+        <v>6511.14</v>
       </c>
     </row>
     <row r="44">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>7798.24</v>
+        <v>7885.46</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2467-466-CM26</t>
+          <t>5522-39-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3162,27 +3162,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>MARCELO FABIAN</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7174.39</v>
+        <v>1789.21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1375758-42-CM26</t>
+          <t>2467-466-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3218,32 +3218,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5637.02</v>
+        <v>7201.57</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5522-39-CM26</t>
+          <t>1375758-42-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3279,17 +3279,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1782.46</v>
+        <v>5658.37</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>66743.77</v>
+        <v>66575.25999999999</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>13179.03</v>
+        <v>13145.76</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>61271.78</v>
+        <v>61853.9</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>55673.9</v>
+        <v>56088.66</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>12526.21</v>
+        <v>12619.53</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>6628.51</v>
+        <v>6677.89</v>
       </c>
     </row>
     <row r="54">
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1806.8</v>
+        <v>1788.78</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2467-533-CM26</t>
+          <t>745-19-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3767,32 +3767,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>SOCIEDAD DE TRANSPORTE JIMÉNEZ HERMANOS LTDA.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>623.86</v>
+        <v>22582.33</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>750-42-CM26</t>
+          <t>3517-70-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3828,32 +3828,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>LUCANO RENT A CAR S.A.</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.813.177-5</t>
+          <t>76.336.696-0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2508.81</v>
+        <v>8873.209999999999</v>
       </c>
     </row>
     <row r="57">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>23862.63</v>
+        <v>23758.03</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3517-70-CM26</t>
+          <t>750-42-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3950,32 +3950,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>LUCANO RENT A CAR S.A.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
+          <t>76.813.177-5</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8912.280000000001</v>
+        <v>2497.81</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>745-19-CM26</t>
+          <t>2467-533-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4011,32 +4011,32 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE TRANSPORTE JIMÉNEZ HERMANOS LTDA.</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>22681.75</v>
+        <v>621.12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>162-194-CM26</t>
+          <t>2467-534-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4072,32 +4072,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Vivanet</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>40831.61</v>
+        <v>10269.86</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>511077-46-CM26</t>
+          <t>2102-388-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,27 +4138,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>Transportes Myriam y Sergio Ltda.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.343.454-0</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4344.74</v>
+        <v>38082.22</v>
       </c>
     </row>
     <row r="62">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>38501.05</v>
+        <v>38082.22</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2102-388-CM26</t>
+          <t>511077-46-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4260,27 +4260,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Transportes Myriam y Sergio Ltda.</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.343.454-0</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>38501.05</v>
+        <v>4297.47</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2467-534-CM26</t>
+          <t>162-194-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4316,32 +4316,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>Vivanet</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.018.259-1</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>10382.81</v>
+        <v>40387.43</v>
       </c>
     </row>
     <row r="65">
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8321.84</v>
+        <v>8302.950000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2291-879-CM26</t>
+          <t>615-25-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4443,27 +4443,27 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.802.006-1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>Ministerio de Vivienda y Urbanismo</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>MARPACIFICO SPA</t>
+          <t>ALEJANDRO BRAULIO PARRA TAMAYO</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.173.533-9</t>
+          <t>10.521.479-0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>43072.51</v>
+        <v>10001.56</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>930-85-CM26</t>
+          <t>1121-47-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4504,27 +4504,27 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1737.89</v>
+        <v>75.23</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1121-47-CM26</t>
+          <t>930-85-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4565,27 +4565,27 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>75.42</v>
+        <v>1733.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>615-25-CM26</t>
+          <t>2291-879-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4626,27 +4626,27 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.802.006-1</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ALEJANDRO BRAULIO PARRA TAMAYO</t>
+          <t>MARPACIFICO SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>10.521.479-0</t>
+          <t>77.173.533-9</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>10026.31</v>
+        <v>42966.15</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>23171.93</v>
+        <v>23285.75</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>52860.96</v>
+        <v>53120.63</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>15219.05</v>
+        <v>15269.54</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1667.6</v>
+        <v>1673.13</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2932.6</v>
+        <v>2941.94</v>
       </c>
     </row>
     <row r="75">
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>26736.84</v>
+        <v>26821.94</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3446-118-CM26</t>
+          <t>1434-94-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5048,32 +5048,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.101.028-1</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección General de Aeronáutica Civil</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R y R LIMITADA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>10750.44</v>
+        <v>403185.16</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1434-94-CM26</t>
+          <t>3446-118-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.101.028-1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>AUTOMOTRIZ R y R LIMITADA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>401052.58</v>
+        <v>10807.6</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>36514.69</v>
+        <v>36943.03</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>53111.95</v>
+        <v>53610.1</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>65088.11</v>
+        <v>64684.58</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>27894.91</v>
+        <v>27721.96</v>
       </c>
     </row>
     <row r="82">
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>25437.68</v>
+        <v>25279.97</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4451-352-CM26</t>
+          <t>2771-286-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5475,32 +5475,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.264.700-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>TRANSPORTES TOGUITA SPA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>77.549.439-5</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>64756.16</v>
+        <v>104061.33</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3710-375-CM26</t>
+          <t>1485217-83-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5541,27 +5541,27 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>15.552.949-0</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>7637.95</v>
+        <v>1593.87</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2771-366-CM26</t>
+          <t>3710-375-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5597,32 +5597,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.264.700-9</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>INVERSIONES LOF SPA</t>
+          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.498.695-2</t>
+          <t>15.552.949-0</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>10624.49</v>
+        <v>7690.68</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2771-286-CM26</t>
+          <t>4451-352-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5658,32 +5658,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>69.264.700-9</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSPORTES TOGUITA SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>77.549.439-5</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>103347.8</v>
+        <v>65203.25</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1485217-83-CM26</t>
+          <t>2771-366-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5719,32 +5719,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.264.700-9</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
+          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>INVERSIONES LOF SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>77.498.695-2</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1582.94</v>
+        <v>10697.85</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>8717.219999999999</v>
+        <v>8777.41</v>
       </c>
     </row>
     <row r="89">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>66151.25</v>
+        <v>66607.96000000001</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1392-57-CM26</t>
+          <t>3477-444-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5907,27 +5907,27 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R y R LIMITADA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>11980.56</v>
+        <v>27231.85</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1078629-11-CM26</t>
+          <t>2467-743-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5963,32 +5963,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SEREMI LA ARAUCANIA FONDOS EXTRAPRESUPUESTARIOS</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>22138.31</v>
+        <v>1379.08</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3477-444-CM26</t>
+          <t>1392-57-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6029,27 +6029,27 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>AUTOMOTRIZ R y R LIMITADA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>27147.91</v>
+        <v>12017.6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2467-743-CM26</t>
+          <t>1078629-11-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6085,32 +6085,32 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SEREMI LA ARAUCANIA FONDOS EXTRAPRESUPUESTARIOS</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1374.83</v>
+        <v>22206.75</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2360-405-CM26</t>
+          <t>997-77-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6151,27 +6151,27 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>17934.88</v>
+        <v>33120.62</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>748-51-CM26</t>
+          <t>1525570-26-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6212,27 +6212,27 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>65.229.008-6</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNIT</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1379.63</v>
+        <v>1909.96</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4404-131-CM26</t>
+          <t>1413021-18-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6273,27 +6273,27 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>60.804.011-0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>DIRECCIÓN REGIONAL ADUANA SAN ANTONIO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>MARPACIFICO SPA</t>
+          <t xml:space="preserve">FELIPE </t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.173.533-9</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8608.190000000001</v>
+        <v>21959.86</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4057-471-CM26</t>
+          <t>2467-740-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6334,27 +6334,27 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.181.100-k</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>22138.97</v>
+        <v>908.83</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1196-138-CM26</t>
+          <t>4057-471-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6395,27 +6395,27 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.181.100-k</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.336.696-0</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>6929.5</v>
+        <v>22080.42</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1413021-18-CM26</t>
+          <t>4404-131-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,27 +6456,27 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>60.804.011-0</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">FELIPE </t>
+          <t>MARPACIFICO SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>77.173.533-9</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>22018.09</v>
+        <v>8585.42</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1525570-26-CM26</t>
+          <t>1196-138-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6517,27 +6517,27 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>65.229.008-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNIT</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1915.02</v>
+        <v>6911.17</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>997-77-CM26</t>
+          <t>748-51-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6578,27 +6578,27 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>33208.45</v>
+        <v>1375.98</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2467-740-CM26</t>
+          <t>2360-405-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6639,27 +6639,27 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>911.24</v>
+        <v>17887.44</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1162.3</v>
+        <v>1146.81</v>
       </c>
     </row>
     <row r="104">
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>11069.49</v>
+        <v>10922.04</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2416-170-CM26</t>
+          <t>4794-74-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6817,32 +6817,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TRANSPORTES SANTIAGO S A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>78.621.600-1</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2213.9</v>
+        <v>75752.64</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2416-171-CM26</t>
+          <t>299-107-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6878,32 +6878,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1372.62</v>
+        <v>1627.92</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>299-107-CM26</t>
+          <t>2416-170-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6939,32 +6939,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1660.42</v>
+        <v>2170.56</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>4794-74-CM26</t>
+          <t>2416-171-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7000,32 +7000,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>TRANSPORTES SANTIAGO S A</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>78.621.600-1</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>77265.00999999999</v>
+        <v>1345.75</v>
       </c>
     </row>
     <row r="109">
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1649.35</v>
+        <v>1624.92</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1062807-63-CM26</t>
+          <t>2546-635-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7127,27 +7127,27 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>221389.72</v>
+        <v>11709.35</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>934-85-CM26</t>
+          <t>4215-17-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>Dirección General de Aeronáutica Civil</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>31880.12</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="112">
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1660.42</v>
+        <v>1626.3</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4215-17-CM26</t>
+          <t>934-85-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>77.48999999999999</v>
+        <v>31224.93</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2546-635-CM26</t>
+          <t>1062807-63-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7371,27 +7371,27 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>11955.05</v>
+        <v>216839.78</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2467-779-CM26</t>
+          <t>1090-57-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7432,27 +7432,27 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>Cesar Ramirez e hijo limitada</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>77.991.710-k</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2142.93</v>
+        <v>17420.11</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1057417-13722-CM26</t>
+          <t>934-86-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7493,27 +7493,27 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.735.787-7</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>40049.63</v>
+        <v>6939.85</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>934-86-CM26</t>
+          <t>2467-779-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7554,27 +7554,27 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76.735.787-7</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7584,13 +7584,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>6874.55</v>
+        <v>2163.28</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1090-57-CM26</t>
+          <t>1057417-13722-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7615,27 +7615,27 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Cesar Ramirez e hijo limitada</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.991.710-k</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>17256.2</v>
+        <v>40430.05</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2792.79</v>
+        <v>2803.69</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2628.44</v>
+        <v>2638.7</v>
       </c>
     </row>
     <row r="121">
@@ -7828,13 +7828,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>20782.62</v>
+        <v>20863.75</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2446-774-CM26</t>
+          <t>1549-2913-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7859,27 +7859,27 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Vivanet</t>
+          <t>OSSAFERNANDEZ SPA</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
+          <t>76.725.099-1</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>13958.77</v>
+        <v>29292.43</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1549-2913-CM26</t>
+          <t>2291-1167-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7920,27 +7920,27 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>OSSAFERNANDEZ SPA</t>
+          <t>MARPACIFICO SPA</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.725.099-1</t>
+          <t>77.173.533-9</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>29002.01</v>
+        <v>4166.03</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>5485-464-CM26</t>
+          <t>2446-774-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7981,27 +7981,27 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>Vivanet</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.018.259-1</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>404.95</v>
+        <v>14098.55</v>
       </c>
     </row>
     <row r="125">
@@ -8072,13 +8072,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>13264.39</v>
+        <v>13397.22</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2291-1167-CM26</t>
+          <t>5485-464-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8103,27 +8103,27 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>MARPACIFICO SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>77.173.533-9</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4124.73</v>
+        <v>409.01</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>10430.41</v>
+        <v>10483.56</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>857.17</v>
+        <v>861.54</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1879.22</v>
+        <v>1888.8</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>48107.72</v>
+        <v>48352.86</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>97.75</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="132">
@@ -8499,13 +8499,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>12825.33</v>
+        <v>12890.69</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>934-88-CM26</t>
+          <t>2409-608-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8530,27 +8530,27 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>8571.700000000001</v>
+        <v>5391.65</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2409-646-CM26</t>
+          <t>2791-98-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8591,27 +8591,27 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>69.170.101-8</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>Iluste Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>78.973.230-2</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,13 +8621,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>12352.71</v>
+        <v>27432.71</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2409-608-CM26</t>
+          <t>2409-646-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8682,13 +8682,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>5370.74</v>
+        <v>12400.79</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2791-98-CM26</t>
+          <t>934-88-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8713,27 +8713,27 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>27326.34</v>
+        <v>8605.07</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1057536-1747-CM26</t>
+          <t>752-187-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>TAXI PETROHUE LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>76.384.260-6</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>25715.11</v>
+        <v>19108.48</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1057536-1856-CM26</t>
+          <t>1153624-91-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8835,27 +8835,27 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>TAXI PETROHUE LIMITADA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>76.384.260-6</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>37586.6</v>
+        <v>427.48</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1153624-91-CM26</t>
+          <t>1057536-1747-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8896,27 +8896,27 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>TAXI PETROHUE LIMITADA</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.384.260-6</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>429.66</v>
+        <v>25584.85</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>752-187-CM26</t>
+          <t>1057536-1856-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TAXI PETROHUE LIMITADA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.384.260-6</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>19205.77</v>
+        <v>37396.2</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>46016.52</v>
+        <v>46114.6</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3759.52</v>
+        <v>3767.53</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>13963.93</v>
+        <v>13993.69</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>3510.32</v>
+        <v>3517.8</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>214.83</v>
+        <v>216.23</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>193131.89</v>
+        <v>194424.62</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>9667.34</v>
+        <v>9732.040000000001</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>4833.67</v>
+        <v>4866.02</v>
       </c>
     </row>
     <row r="149">
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>12245.28</v>
+        <v>12330.98</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2792-412-CM26</t>
+          <t>930-147-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9567,27 +9567,27 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>32224.45</v>
+        <v>5139.63</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2078-924-CM26</t>
+          <t>2792-412-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9628,27 +9628,27 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>Iluste Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>CAROLYN MARLEN</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.905.851-6</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>16112.23</v>
+        <v>32122.67</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2424-948-CM26</t>
+          <t>2078-924-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9689,27 +9689,27 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>EMPRESA DE TRANSPORTES FUENTES MENDOZA LIMITADA</t>
+          <t>CAROLYN MARLEN</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>77.196.907-0</t>
+          <t>76.905.851-6</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>14286.17</v>
+        <v>16061.33</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>930-147-CM26</t>
+          <t>2424-948-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9750,27 +9750,27 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>EMPRESA DE TRANSPORTES FUENTES MENDOZA LIMITADA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>77.196.907-0</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>5155.91</v>
+        <v>14241.05</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1278.24</v>
+        <v>1275.46</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>64448.86</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>6015.23</v>
+        <v>6002.14</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>46725.46</v>
+        <v>46631.79</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1278.24</v>
+        <v>1275.67</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>7218.28</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>5152.57</v>
+        <v>5142.24</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>18153.11</v>
+        <v>18116.72</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>144.53</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>47933.88</v>
+        <v>47837.79</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>9357.610000000001</v>
+        <v>9303.450000000001</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>526.33</v>
+        <v>517.84</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>10182.93</v>
+        <v>10018.6</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>44061.57</v>
+        <v>43355.11</v>
       </c>
     </row>
     <row r="168">
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1074.15</v>
+        <v>1061.65</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4358-141-CM26</t>
+          <t>2407-490-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10726,27 +10726,27 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>9183.969999999999</v>
+        <v>7638.09</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2407-490-CM26</t>
+          <t>4358-141-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10787,27 +10787,27 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>7680.67</v>
+        <v>9133.049999999999</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>4886-97-CM26</t>
+          <t>2467-894-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>212.68</v>
+        <v>1817.07</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2467-894-CM26</t>
+          <t>4886-97-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>Subsecretaria de las Culturas y las Artes Región del Biobio</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1826.05</v>
+        <v>211.64</v>
       </c>
     </row>
     <row r="173">
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>6586.68</v>
+        <v>6554.29</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1549-3384-CM26</t>
+          <t>1057417-14563-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11031,27 +11031,27 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>11278.56</v>
+        <v>43703.37</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1057417-14563-CM26</t>
+          <t>1549-3384-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11092,27 +11092,27 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>43412.78</v>
+        <v>11354.05</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,4521 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>16477.44</v>
+        <v>16587.73</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1306643-258-CM26</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>69.254.200-2</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>156443.2</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1488-903-CM26</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>61.602.232-6</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>TRANSERVI JL SPA</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>208859.42</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1488-904-CM26</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>61.602.232-6</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>TRANSERVI JL SPA</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>83035.34</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1178-45-CM26</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>61.202.000-0</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>INVERSIONES MTEA SPA</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>76.366.361-2</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>183957.01</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>932-136-CM26</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>76.036.979-9</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>2350.12</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>934-114-CM26</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>PAULA ANDREA MERY NAVIA</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>2594.9</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1390255-11-CM26</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>65.165.009-7</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Cesar Ramirez e hijo limitada</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>77.991.710-k</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>48115.83</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>4451-470-CM26</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>TRANSPORTES TOGUITA SPA</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>77.549.439-5</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>6031.07</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>564953-778-CM26</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>70.902.000-5</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Corporación de Educación y Salud de Las Condes</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>5594.68</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1375758-63-CM26</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>61.981.300-6</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>11321</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1134432-566-CM26</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>9720.629999999999</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1057439-4946-CM26</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>61.606.402-9</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Itravel -  Transporte Privado de Pasajeros</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>76.935.610-k</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M188" s="2" t="n">
+        <v>12669.88</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1153624-116-CM26</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>62.000.670-K</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M189" s="2" t="n">
+        <v>327.07</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>511077-95-CM26</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>60.703.000-6</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>83.547.100-4</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>5049.19</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2408-724-CM26</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>14179.41</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>3517-127-CM26</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>69.180.700-2</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>76.336.696-0</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>8099.82</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>675-43-CM26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>61.402.019-9</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>David Isaac</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>10942.6</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1305532-62-CM26</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>61.981.040-6</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>VIVANET</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>76.018.259-1</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>14925.7</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1658-2266-CM26</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>69.190.700-7</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>TRANSPORTES ALV-BAACK SPA</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>77.314.274-2</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>16359.18</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>932-138-CM26</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>76.036.979-9</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>21934.59</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1057417-14549-CM26</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Transportes Luis Rifo y compañia limitada</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>76.114.087-6</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>37143.95</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1057417-14604-CM26</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Transportes Luis Rifo y compañia limitada</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>76.114.087-6</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>3535.96</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1197-97-CM26</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Transporte Corporativo Infinity</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>76.207.531-8</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>15278.84</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2852-777-CM26</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>76.238.635-6</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>6558.98</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1860-62-CM26</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>8202.01</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1057439-5370-CM26</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>61.606.402-9</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Itravel -  Transporte Privado de Pasajeros</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>76.935.610-k</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>3128.84</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>934-131-CM26</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>PAULA ANDREA MERY NAVIA</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>2960.53</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>4081-278-CM26</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>69.151.001-8</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>4385.96</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2446-925-CM26</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>69.040.300-5</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>VIVANET</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>76.018.259-1</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>14473.68</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2546-726-CM26</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>8.148.859-2</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="n">
+        <v>71178.27</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1057062-368-CM26</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>TRANSPORTES SURAY LIMITADA.</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>77.799.670-3</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="n">
+        <v>2354.36</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2792-553-CM26</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>69.255.400-0</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Municipalidad de Huechuraba</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>FEBGIP SPA</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="n">
+        <v>29566.36</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1443565-35-CM26</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>61.312.000-9</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>INIA</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="n">
+        <v>20457.74</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1443565-36-CM26</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>61.312.000-9</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>INIA</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Región de Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>83.547.100-4</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="n">
+        <v>3065.85</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>4358-167-CM26</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>69.170.701-6</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="n">
+        <v>3821.94</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1197-99-CM26</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>CAR PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="n">
+        <v>27355.86</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>1523-1816-CM26</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>61.602.236-9</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>16.995.419-4</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="n">
+        <v>249028.09</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>934-134-CM26</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>PAULA ANDREA MERY NAVIA</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="n">
+        <v>3942.4</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>4451-503-CM26</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>TRANSPORTES TOGUITA SPA</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>77.549.439-5</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="n">
+        <v>6504.94</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1375758-74-CM26</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>61.981.300-6</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="n">
+        <v>9308.790000000001</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>545774-39-CM26</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>69.070.800-0</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="n">
+        <v>39379.12</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1208093-61-CM26</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="n">
+        <v>4375.46</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>1080089-504-CM26</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>61.607.900-k</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>TRANSPORTES, RENT A CAR Y LOGÍSTICA RAMÓN VILLABLANCA BARRIENTOS E.I.R</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>77.551.961-4</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="n">
+        <v>8458.77</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1134432-587-CM26</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="n">
+        <v>3730.53</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>1385462-131-CM26</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="n">
+        <v>11707.46</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>1495207-11-CM26</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="n">
+        <v>11707.46</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>1495208-17-CM26</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="n">
+        <v>11707.46</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>934-136-CM26</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>77.659.446-6</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="n">
+        <v>878.41</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2408-777-CM26</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>69.170.100-K</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Bío-Bío</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="n">
+        <v>10663.29</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>1134432-597-CM26</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>69.060.800-6</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="n">
+        <v>303.28</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>1057499-434-CM26</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>61.608.108-K</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esteban jesus </t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>76.252.815-0</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="n">
+        <v>62389.65</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>3894-78-CM26</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>69.071.400-0</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="n">
+        <v>21782.46</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>1260-124-CM26</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>61.923.200-3</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="n">
+        <v>26138.95</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>1198-203-CM26</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="n">
+        <v>5193.3</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>1078634-13-CM26</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>61.402.010-5</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Región de Los Ríos</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>David Isaac</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="n">
+        <v>43733.05</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>5522-84-CM26</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="n">
+        <v>8801.280000000001</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2291-1414-CM26</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>MARPACIFICO SPA</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>77.173.533-9</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="n">
+        <v>6978.05</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2291-1412-CM26</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rentur Chile SpA </t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>76.241.697-2</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="n">
+        <v>5705.32</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>1658-2410-CM26</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>69.190.700-7</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>TRANSPORTES ALV-BAACK SPA</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>77.314.274-2</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="n">
+        <v>41604.95</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>1057417-15339-CM26</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="n">
+        <v>42076.74</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>1057539-4659-CM26</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>PAULA ANDREA MERY NAVIA</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="n">
+        <v>62192.68</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>660-24-CM26</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>61.834.000-7</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Patricio Osvaldo</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>76.845.503-1</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="n">
+        <v>79190.19</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>967490-77-CM26</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>60.505.000-K</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>76.310.505-9</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="n">
+        <v>11737.55</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>1057499-443-CM26</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>61.608.108-K</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="n">
+        <v>20687.7</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>1057499-444-CM26</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>61.608.108-K</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="n">
+        <v>9472.790000000001</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>1057499-445-CM26</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>61.608.108-K</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="n">
+        <v>9554.450000000001</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>3474-488-CM26</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>61.979.960-7</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>78.973.230-2</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="n">
+        <v>33034.99</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>4650-122-CM26</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Marcelo Fabian</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>76.621.909-8</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="n">
+        <v>272.21</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>932-152-CM26</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>76.036.979-9</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="n">
+        <v>17149.02</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>1443565-45-CM26</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>61.312.000-9</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>INIA</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Región de Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="n">
+        <v>408.91</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>932-155-CM26</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>CAR PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="n">
+        <v>35882.19</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>1305532-73-CM26</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>61.981.040-6</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Coquimbo </t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>VIVANET</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>76.018.259-1</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="n">
+        <v>12914.61</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1197-107-CM26</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="n">
+        <v>1452.68</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2793-854-CM26</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>69.255.400-0</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Municipalidad de Huechuraba</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="n">
+        <v>36806.65</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/todos.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/todos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="transporte-privado-d todos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="transporte-privado-d todos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/todos.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/todos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M329"/>
+  <dimension ref="A1:M330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1920,7 +1920,11 @@
           <t>78.973.230-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2542,7 +2546,11 @@
           <t>78.973.230-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9047,7 +9055,11 @@
           <t>78.973.230-2</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10678,7 +10690,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1485217-105-CM26</t>
+          <t>3134-146-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10698,48 +10710,52 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>TRAVEL RENT A CAR LIMITADA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
+          <t>77.854.171-8</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>7203.81</v>
+        <v>5142.24</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3134-146-CM26</t>
+          <t>1485217-105-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10759,46 +10775,42 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>TRAVEL RENT A CAR LIMITADA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>77.854.171-8</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Magallanes</t>
-        </is>
-      </c>
+          <t>76.310.505-9</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>5142.24</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="168">
@@ -15621,7 +15633,11 @@
           <t>78.973.230-2</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15634,7 +15650,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1057499-445-CM26</t>
+          <t>1057499-444-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15693,13 +15709,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>9554.450000000001</v>
+        <v>9472.790000000001</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1057499-443-CM26</t>
+          <t>1057499-445-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15758,13 +15774,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>20687.7</v>
+        <v>9554.450000000001</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1057499-444-CM26</t>
+          <t>967490-77-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15784,17 +15800,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15804,32 +15820,28 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.310.505-9</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>9472.790000000001</v>
+        <v>11737.55</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>967490-77-CM26</t>
+          <t>660-24-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15849,32 +15861,32 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.834.000-7</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>Patricio Osvaldo</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>76.845.503-1</t>
         </is>
       </c>
       <c r="K249" t="inlineStr"/>
@@ -15884,13 +15896,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>11737.55</v>
+        <v>79190.19</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>660-24-CM26</t>
+          <t>1057539-4659-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15915,43 +15927,47 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.834.000-7</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Patricio Osvaldo</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>76.845.503-1</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>79190.19</v>
+        <v>62192.68</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1057539-4659-CM26</t>
+          <t>1057499-443-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -15976,32 +15992,32 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -16010,7 +16026,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>62192.68</v>
+        <v>20687.7</v>
       </c>
     </row>
     <row r="252">
@@ -16138,7 +16154,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1305532-73-CM26</t>
+          <t>2793-854-CM26</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16163,43 +16179,47 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>VIVANET</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>12914.61</v>
+        <v>36806.65</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2793-854-CM26</t>
+          <t>1197-107-CM26</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16224,47 +16244,43 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>36806.65</v>
+        <v>1452.68</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1197-107-CM26</t>
+          <t>1305532-73-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16289,27 +16305,27 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.018.259-1</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -16319,13 +16335,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1452.68</v>
+        <v>12914.61</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1495199-11-CM26</t>
+          <t>1385462-164-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16360,7 +16376,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16390,7 +16406,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1388961-663-CM26</t>
+          <t>2085-746-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16415,27 +16431,27 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>65.118.035-K</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>76.336.696-0</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -16445,13 +16461,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>8793.049999999999</v>
+        <v>19927.15</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>838794-185-CM26</t>
+          <t>1079576-942-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16476,43 +16492,47 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.980.420-1</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>SERVICIOS LOGÍSTICOS  Y TRANSPORTES VIÑA DEL MAR SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>76.345.484-3</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>6856.65</v>
+        <v>6342.49</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1398-1092-CM26</t>
+          <t>1388961-663-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16537,47 +16557,43 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>65.118.035-K</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>ABRAHAM PATRICIO VILLANUEVA MICHEA</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>15.751.336-2</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>77.951.690-3</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>8873.370000000001</v>
+        <v>8793.049999999999</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1079576-942-CM26</t>
+          <t>838794-185-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16602,47 +16618,43 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.980.420-1</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>SERVICIOS LOGÍSTICOS  Y TRANSPORTES VIÑA DEL MAR SPA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.345.484-3</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>6342.49</v>
+        <v>6856.65</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2085-746-CM26</t>
+          <t>1495199-11-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16667,43 +16679,47 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>19927.15</v>
+        <v>13606.17</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1385462-164-CM26</t>
+          <t>1398-1092-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16728,32 +16744,32 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>ABRAHAM PATRICIO VILLANUEVA MICHEA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>15.751.336-2</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -16762,13 +16778,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>13606.17</v>
+        <v>8873.370000000001</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>5056-3060-CM26</t>
+          <t>5485-620-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16793,41 +16809,37 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>ABRAHAM PATRICIO VILLANUEVA MICHEA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>15.751.336-2</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>5334.84</v>
+        <v>301.09</v>
       </c>
     </row>
     <row r="265">
@@ -16955,7 +16967,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5485-620-CM26</t>
+          <t>5056-3060-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16980,43 +16992,47 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>ABRAHAM PATRICIO VILLANUEVA MICHEA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr"/>
+          <t>15.751.336-2</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>301.09</v>
+        <v>5334.84</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1057627-19-CM26</t>
+          <t>1057532-1385-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17041,43 +17057,47 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.607.101-7</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>3417.63</v>
+        <v>7476.08</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1057532-1385-CM26</t>
+          <t>1057627-19-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17102,41 +17122,37 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.607.101-7</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>12.382.191-2</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>7476.08</v>
+        <v>3417.63</v>
       </c>
     </row>
     <row r="270">
@@ -17386,7 +17402,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1469-2627-CM26</t>
+          <t>2490-186-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17411,27 +17427,27 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>BUSES VILLAR</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>76.465.610-5</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17441,13 +17457,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>56713.22</v>
+        <v>5628.54</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>3316-189-CM26</t>
+          <t>1469-2627-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17467,32 +17483,32 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>BUSES VILLAR</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>76.465.610-5</t>
         </is>
       </c>
       <c r="K275" t="inlineStr"/>
@@ -17502,13 +17518,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>15283.35</v>
+        <v>56713.22</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2490-186-CM26</t>
+          <t>3316-189-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17528,17 +17544,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17548,12 +17564,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -17563,7 +17579,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>5628.54</v>
+        <v>15283.35</v>
       </c>
     </row>
     <row r="277">
@@ -17935,7 +17951,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1134432-647-CM26</t>
+          <t>5522-93-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -17955,52 +17971,48 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>ALIMENTOS SOL DE QUILLOTA SPA</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>77.850.715-3</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>83.547.100-4</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1440.51</v>
+        <v>4534.31</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5522-93-CM26</t>
+          <t>5485-657-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18040,12 +18052,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -18055,13 +18067,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>4534.31</v>
+        <v>300.99</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>5485-657-CM26</t>
+          <t>1134432-647-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18081,48 +18093,52 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>ALIMENTOS SOL DE QUILLOTA SPA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
-        </is>
-      </c>
-      <c r="K285" t="inlineStr"/>
+          <t>77.850.715-3</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>300.99</v>
+        <v>1440.51</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>933-88-CM26</t>
+          <t>931-165-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18157,17 +18173,17 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K286" t="inlineStr"/>
@@ -18177,13 +18193,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>3841.35</v>
+        <v>20647.27</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>931-165-CM26</t>
+          <t>933-88-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18218,17 +18234,17 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K287" t="inlineStr"/>
@@ -18238,13 +18254,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>20647.27</v>
+        <v>3841.35</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>933-70-CM26</t>
+          <t>2467-1158-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18264,48 +18280,52 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>INVERSIONES LOF SPA</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>77.498.695-2</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
           <t>Biobío</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t>76.470.279-4</t>
-        </is>
-      </c>
-      <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>85024.07000000001</v>
+        <v>6450.14</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2123-317-CM26</t>
+          <t>1300-294-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -18325,32 +18345,32 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>76.076.244-k</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K289" t="inlineStr"/>
@@ -18360,13 +18380,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>10096.61</v>
+        <v>637.6799999999999</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2427-833-CM26</t>
+          <t>836-153-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18391,12 +18411,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18406,12 +18426,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.076.244-k</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
@@ -18421,13 +18441,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>7452.57</v>
+        <v>75458.86</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>836-153-CM26</t>
+          <t>2123-317-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18452,12 +18472,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18482,13 +18502,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>75458.86</v>
+        <v>10096.61</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1300-294-CM26</t>
+          <t>933-70-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18513,27 +18533,27 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>61.961.000-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K292" t="inlineStr"/>
@@ -18543,13 +18563,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>637.6799999999999</v>
+        <v>85024.07000000001</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2467-1158-CM26</t>
+          <t>2427-833-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18574,41 +18594,37 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>INVERSIONES LOF SPA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>77.498.695-2</t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>6450.14</v>
+        <v>7452.57</v>
       </c>
     </row>
     <row r="294">
@@ -19049,7 +19065,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1059109-94-CM26</t>
+          <t>2735-1056-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19074,43 +19090,47 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
-        </is>
-      </c>
-      <c r="K301" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>30258.13</v>
+        <v>55142.84</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>813685-229-CM26</t>
+          <t>931-167-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19135,27 +19155,27 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>LUCANO RENT A CAR S.A.</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>76.813.177-5</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K302" t="inlineStr"/>
@@ -19165,13 +19185,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>313.01</v>
+        <v>9912.15</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1197-123-CM26</t>
+          <t>1197-122-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19226,13 +19246,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>6260.3</v>
+        <v>8555.75</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>931-167-CM26</t>
+          <t>1197-123-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19267,17 +19287,17 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K304" t="inlineStr"/>
@@ -19287,13 +19307,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>9912.15</v>
+        <v>6260.3</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2735-1056-CM26</t>
+          <t>813685-229-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19318,47 +19338,43 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>LUCANO RENT A CAR S.A.</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.813.177-5</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>55142.84</v>
+        <v>313.01</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1197-122-CM26</t>
+          <t>1059109-94-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19393,17 +19409,17 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K306" t="inlineStr"/>
@@ -19413,13 +19429,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>8555.75</v>
+        <v>30258.13</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>3073-382-CM26</t>
+          <t>2713-1059-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19444,27 +19460,27 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
@@ -19474,13 +19490,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>10084.03</v>
+        <v>11010</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>5522-94-CM26</t>
+          <t>678-45-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19505,27 +19521,27 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19535,13 +19551,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>15493.7</v>
+        <v>21007.77</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1485217-157-CM26</t>
+          <t>678-46-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19566,27 +19582,27 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>61.402.018-0</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K309" t="inlineStr"/>
@@ -19596,13 +19612,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>10021.01</v>
+        <v>15729.88</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2713-1059-CM26</t>
+          <t>1485217-157-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19627,27 +19643,27 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -19657,13 +19673,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>11010</v>
+        <v>10021.01</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>678-45-CM26</t>
+          <t>3073-382-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19688,27 +19704,27 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K311" t="inlineStr"/>
@@ -19718,13 +19734,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>21007.77</v>
+        <v>10084.03</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>678-46-CM26</t>
+          <t>5522-94-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -19749,27 +19765,27 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>61.402.018-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K312" t="inlineStr"/>
@@ -19779,7 +19795,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>15729.88</v>
+        <v>15493.7</v>
       </c>
     </row>
     <row r="313">
@@ -20216,7 +20232,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2467-1224-CM26</t>
+          <t>3192-95-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -20241,27 +20257,27 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.102.090-2</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K320" t="inlineStr"/>
@@ -20271,13 +20287,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>1625.75</v>
+        <v>4028.12</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>3192-95-CM26</t>
+          <t>2467-1224-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -20302,27 +20318,27 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>61.102.090-2</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K321" t="inlineStr"/>
@@ -20332,7 +20348,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>4028.12</v>
+        <v>1625.75</v>
       </c>
     </row>
     <row r="322">
@@ -20399,7 +20415,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1469-2823-CM26</t>
+          <t>188-635-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20424,47 +20440,43 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>70.933.700-9</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>933.51</v>
+        <v>12369.05</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>188-635-CM26</t>
+          <t>1469-2823-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20489,43 +20501,47 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
-        </is>
-      </c>
-      <c r="K324" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>12369.05</v>
+        <v>933.51</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1121-106-CM26</t>
+          <t>2427-889-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -20550,27 +20566,27 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.076.244-k</t>
         </is>
       </c>
       <c r="K325" t="inlineStr"/>
@@ -20580,13 +20596,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>165.18</v>
+        <v>32577.09</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2427-889-CM26</t>
+          <t>1121-106-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20611,27 +20627,27 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>76.076.244-k</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K326" t="inlineStr"/>
@@ -20641,13 +20657,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>32577.09</v>
+        <v>165.18</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>615-72-CM26</t>
+          <t>1300-317-SE26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20672,43 +20688,47 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>61.802.006-1</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>VERÓNICA LOURDES SANDOVAL VALENZUELA</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>12.690.978-0</t>
-        </is>
-      </c>
-      <c r="K327" t="inlineStr"/>
+          <t>78.973.230-2</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>30937.4</v>
+        <v>866.25</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>973155-2-CM26</t>
+          <t>615-72-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20733,12 +20753,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>60.803.435-8</t>
+          <t>61.802.006-1</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20748,12 +20768,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t>VERÓNICA LOURDES SANDOVAL VALENZUELA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>12.690.978-0</t>
         </is>
       </c>
       <c r="K328" t="inlineStr"/>
@@ -20763,13 +20783,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>618.75</v>
+        <v>30937.4</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1059109-101-CM26</t>
+          <t>973155-2-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -20784,7 +20804,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -20794,27 +20814,27 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.803.435-8</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K329" t="inlineStr"/>
@@ -20824,6 +20844,67 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
+        <v>618.75</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>1059109-101-CM26</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M330" s="2" t="n">
         <v>926.26</v>
       </c>
     </row>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/todos.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/todos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M376"/>
+  <dimension ref="A1:M378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2205,7 +2205,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1121-36-CM26</t>
+          <t>2360-190-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2225,32 +2225,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>202.82</v>
+        <v>3519.28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2360-190-CM26</t>
+          <t>1121-36-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2286,32 +2286,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3519.28</v>
+        <v>202.82</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1161266-265-CM26</t>
+          <t>4766-3470-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2352,27 +2352,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.141.800-6</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TUCAPEL</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>SERVICIOS LOGÍSTICOS  Y TRANSPORTES VIÑA DEL MAR SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.345.484-3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2382,13 +2382,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>25721.89</v>
+        <v>11155.47</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4766-3470-CM26</t>
+          <t>1161266-265-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2413,27 +2413,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>69.141.800-6</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SERVICIOS LOGÍSTICOS  Y TRANSPORTES VIÑA DEL MAR SPA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.345.484-3</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>11155.47</v>
+        <v>25721.89</v>
       </c>
     </row>
     <row r="33">
@@ -2766,7 +2766,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5522-31-CM26</t>
+          <t>748-33-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2786,32 +2786,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2821,7 +2821,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>8461.450000000001</v>
+        <v>22350.92</v>
       </c>
     </row>
     <row r="39">
@@ -2888,7 +2888,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>748-33-CM26</t>
+          <t>5522-31-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2908,32 +2908,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>22350.92</v>
+        <v>8461.450000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3201,7 +3201,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5522-39-CM26</t>
+          <t>1375758-42-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3256,13 +3256,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1789.21</v>
+        <v>5658.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2467-466-CM26</t>
+          <t>5522-39-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3287,27 +3287,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3317,13 +3317,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7201.57</v>
+        <v>1789.21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1375758-42-CM26</t>
+          <t>2467-466-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3343,32 +3343,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5658.37</v>
+        <v>7201.57</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4454-395-CM26</t>
+          <t>1030177-70-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3409,17 +3409,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.150.600-2</t>
+          <t>69.141.400-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3439,13 +3439,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>13145.76</v>
+        <v>66575.25999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1030177-70-CM26</t>
+          <t>4454-395-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3470,17 +3470,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.141.400-0</t>
+          <t>69.150.600-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>66575.25999999999</v>
+        <v>13145.76</v>
       </c>
     </row>
     <row r="50">
@@ -3567,7 +3567,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2307-603-CM26</t>
+          <t>4766-3491-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3587,32 +3587,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>RENT A CAR SUR LTDA</t>
+          <t>SERVICIOS LOGÍSTICOS  Y TRANSPORTES VIÑA DEL MAR SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.683.282-2</t>
+          <t>76.345.484-3</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3622,13 +3622,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>12619.53</v>
+        <v>6677.89</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4404-54-CM26</t>
+          <t>2307-603-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3648,52 +3648,48 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>MARPACIFICO SPA</t>
+          <t>RENT A CAR SUR LTDA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.173.533-9</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.683.282-2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>56088.66</v>
+        <v>12619.53</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4766-3491-CM26</t>
+          <t>4404-54-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3718,37 +3714,41 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SERVICIOS LOGÍSTICOS  Y TRANSPORTES VIÑA DEL MAR SPA</t>
+          <t>MARPACIFICO SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.345.484-3</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>77.173.533-9</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>6677.89</v>
+        <v>56088.66</v>
       </c>
     </row>
     <row r="54">
@@ -3815,7 +3815,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1176-39-CM26</t>
+          <t>3517-70-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3840,27 +3840,27 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>76.336.696-0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3870,13 +3870,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>23758.03</v>
+        <v>8873.209999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>750-42-CM26</t>
+          <t>1176-39-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3896,32 +3896,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>LUCANO RENT A CAR S.A.</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.813.177-5</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3931,13 +3931,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2497.81</v>
+        <v>23758.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2467-533-CM26</t>
+          <t>750-42-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3957,32 +3957,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>LUCANO RENT A CAR S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.813.177-5</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3992,13 +3992,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>621.12</v>
+        <v>2497.81</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3517-70-CM26</t>
+          <t>2467-533-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4023,27 +4023,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8873.209999999999</v>
+        <v>621.12</v>
       </c>
     </row>
     <row r="59">
@@ -4246,7 +4246,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2102-387-CM26</t>
+          <t>2102-388-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4307,7 +4307,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2102-388-CM26</t>
+          <t>2467-534-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4327,32 +4327,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Transportes Myriam y Sergio Ltda.</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.343.454-0</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4362,13 +4362,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>38082.22</v>
+        <v>10269.86</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2467-534-CM26</t>
+          <t>2102-387-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4388,32 +4388,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>Transportes Myriam y Sergio Ltda.</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.343.454-0</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>10269.86</v>
+        <v>38082.22</v>
       </c>
     </row>
     <row r="65">
@@ -5531,7 +5531,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1485217-83-CM26</t>
+          <t>2771-286-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5556,27 +5556,27 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.264.700-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5586,13 +5586,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1593.87</v>
+        <v>104061.33</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2771-286-CM26</t>
+          <t>934-81-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5617,43 +5617,47 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.264.700-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>104061.33</v>
+        <v>1548.17</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4451-353-CM26</t>
+          <t>1485217-83-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5678,47 +5682,43 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA 9704 SPA</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.171.057-3</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>8777.41</v>
+        <v>1593.87</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>934-81-CM26</t>
+          <t>3710-375-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5743,47 +5743,43 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>15.552.949-0</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1548.17</v>
+        <v>7690.68</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3710-375-CM26</t>
+          <t>4451-352-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5808,43 +5804,47 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
+          <t>TRANSPORTES TOGUITA SPA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>15.552.949-0</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+          <t>77.549.439-5</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>7690.68</v>
+        <v>65203.25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4451-352-CM26</t>
+          <t>2771-366-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5869,32 +5869,32 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.264.700-9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>TRANSPORTES TOGUITA SPA</t>
+          <t>INVERSIONES LOF SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.549.439-5</t>
+          <t>77.498.695-2</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>65203.25</v>
+        <v>10697.85</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2771-366-CM26</t>
+          <t>4451-353-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5934,32 +5934,32 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>69.264.700-9</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIGUAYANTE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>INVERSIONES LOF SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA 9704 SPA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.498.695-2</t>
+          <t>77.171.057-3</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>10697.85</v>
+        <v>8777.41</v>
       </c>
     </row>
     <row r="90">
@@ -6287,7 +6287,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2467-740-CM26</t>
+          <t>1525570-26-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6307,48 +6307,52 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>65.229.008-6</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>908.83</v>
+        <v>1909.96</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1413021-18-CM26</t>
+          <t>997-77-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6373,27 +6377,27 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>60.804.011-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6403,13 +6407,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>21959.86</v>
+        <v>33120.62</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>997-77-CM26</t>
+          <t>2467-740-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6429,32 +6433,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6464,13 +6468,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>33120.62</v>
+        <v>908.83</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1525570-26-CM26</t>
+          <t>4057-471-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6490,46 +6494,42 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>65.229.008-6</t>
+          <t>69.181.100-k</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
+          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.336.696-0</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1909.96</v>
+        <v>22080.42</v>
       </c>
     </row>
     <row r="99">
@@ -6661,7 +6661,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2360-405-CM26</t>
+          <t>748-51-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6681,32 +6681,32 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6716,13 +6716,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>17887.44</v>
+        <v>1375.98</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4057-471-CM26</t>
+          <t>2360-405-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6747,27 +6747,27 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.181.100-k</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONQUIMAY</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6777,13 +6777,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>22080.42</v>
+        <v>17887.44</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>748-51-CM26</t>
+          <t>1413021-18-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6808,27 +6808,27 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>60.804.011-0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6838,7 +6838,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1375.98</v>
+        <v>21959.86</v>
       </c>
     </row>
     <row r="104">
@@ -6966,7 +6966,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2416-170-CM26</t>
+          <t>4794-74-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6991,27 +6991,27 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>TRANSPORTES SANTIAGO S A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>78.621.600-1</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>2170.56</v>
+        <v>75752.64</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2416-171-CM26</t>
+          <t>299-107-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7052,27 +7052,27 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.150.400-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCEPCION</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -7082,13 +7082,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1345.75</v>
+        <v>1627.92</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>299-107-CM26</t>
+          <t>2416-170-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7113,27 +7113,27 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7143,13 +7143,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1627.92</v>
+        <v>2170.56</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4794-74-CM26</t>
+          <t>2416-171-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7174,27 +7174,27 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.150.400-K</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>TRANSPORTES SANTIAGO S A</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>78.621.600-1</t>
+          <t>12.382.191-2</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>75752.64</v>
+        <v>1345.75</v>
       </c>
     </row>
     <row r="110">
@@ -7271,7 +7271,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1062807-63-CM26</t>
+          <t>2546-635-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7291,32 +7291,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7326,13 +7326,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>216839.78</v>
+        <v>11709.35</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>934-85-CM26</t>
+          <t>4215-17-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7357,12 +7357,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7372,28 +7372,32 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>31224.93</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>4215-17-CM26</t>
+          <t>934-82-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7413,17 +7417,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7452,13 +7456,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>75.89</v>
+        <v>1626.3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>934-82-CM26</t>
+          <t>4215-18-SE26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7478,17 +7482,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7517,13 +7521,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1626.3</v>
+        <v>84491.62</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4215-18-SE26</t>
+          <t>934-85-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7548,12 +7552,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7563,32 +7567,28 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>8.148.859-2</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>84491.62</v>
+        <v>31224.93</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2546-635-CM26</t>
+          <t>1062807-63-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7608,32 +7608,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7643,13 +7643,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>11709.35</v>
+        <v>216839.78</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1090-57-CM26</t>
+          <t>934-86-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7669,48 +7669,52 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Cesar Ramirez e hijo limitada</t>
+          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>77.991.710-k</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
+          <t>76.735.787-7</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>17420.11</v>
+        <v>6939.85</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2467-779-CM26</t>
+          <t>1090-57-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7730,32 +7734,32 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>Cesar Ramirez e hijo limitada</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>77.991.710-k</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -7765,7 +7769,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2163.28</v>
+        <v>17420.11</v>
       </c>
     </row>
     <row r="119">
@@ -7836,7 +7840,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>934-86-CM26</t>
+          <t>2467-779-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7861,47 +7865,43 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>76.735.787-7</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.604.912-5</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>6939.85</v>
+        <v>2163.28</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1480972-302-CM26</t>
+          <t>837-410-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7926,43 +7926,47 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.981.050-3</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2638.7</v>
+        <v>2803.69</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>837-410-CM26</t>
+          <t>1060500-16-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7987,47 +7991,43 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>61.003.000-9</t>
+          <t>62.000.510-k</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2803.69</v>
+        <v>20863.75</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1060500-16-CM26</t>
+          <t>1480972-302-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8052,27 +8052,27 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>62.000.510-k</t>
+          <t>61.981.050-3</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -8082,13 +8082,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>20863.75</v>
+        <v>2638.7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2446-774-CM26</t>
+          <t>5485-464-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8108,48 +8108,52 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>69.040.300-5</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COQUIMBO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>VIVANET</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>14098.55</v>
+        <v>409.01</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1480972-301-CM26</t>
+          <t>2291-1167-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8174,43 +8178,47 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>61.981.050-3</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>MARPACIFICO SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
+          <t>77.173.533-9</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>13397.22</v>
+        <v>4166.03</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2291-1167-CM26</t>
+          <t>1549-2913-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8235,47 +8243,43 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>MARPACIFICO SPA</t>
+          <t>OSSAFERNANDEZ SPA</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>77.173.533-9</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.725.099-1</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4166.03</v>
+        <v>29292.43</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1549-2913-CM26</t>
+          <t>2446-774-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8300,27 +8304,27 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>69.040.300-5</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>I MUNICIPALIDAD DE COQUIMBO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>OSSAFERNANDEZ SPA</t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.725.099-1</t>
+          <t>76.018.259-1</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8330,13 +8334,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>29292.43</v>
+        <v>14098.55</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>5485-464-CM26</t>
+          <t>1480972-301-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8356,52 +8360,48 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.050-3</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>409.01</v>
+        <v>13397.22</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>5485-472-CM26</t>
+          <t>652-186-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8426,47 +8426,47 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>98.25</v>
+        <v>12890.69</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1134432-487-CM26</t>
+          <t>5485-472-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8491,43 +8491,47 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1888.8</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>652-186-CM26</t>
+          <t>1134432-487-CM26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8552,47 +8556,43 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>12890.69</v>
+        <v>1888.8</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>4886-60-CM26</t>
+          <t>3553-292-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8617,27 +8617,27 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>53.312.479-8</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>12.382.191-2</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8647,7 +8647,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>861.54</v>
+        <v>48352.86</v>
       </c>
     </row>
     <row r="133">
@@ -8844,7 +8844,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2735-872-SE26</t>
+          <t>4886-60-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8869,47 +8869,43 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>53.312.479-8</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
+          <t>EVARISTO IVÁN OÑATE VÁSQUEZ</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>76.366.537-2</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>12.382.191-2</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>28920.36</v>
+        <v>861.54</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>3553-292-CM26</t>
+          <t>2735-872-SE26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8934,12 +8930,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8949,22 +8945,26 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>48352.86</v>
+        <v>28920.36</v>
       </c>
     </row>
     <row r="138">
@@ -9344,7 +9344,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>1153624-91-CM26</t>
+          <t>752-187-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9369,43 +9369,47 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>72.221.800-0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>JOSUE MANUEL</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>76.370.023-2</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>427.48</v>
+        <v>19108.48</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>752-187-CM26</t>
+          <t>1153624-91-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9430,47 +9434,43 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>72.221.800-0</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DECIMA REGION LOS LAGOS</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.370.023-2</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>19108.48</v>
+        <v>427.48</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2467-824-CM26</t>
+          <t>1196-151-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9490,32 +9490,32 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Roberto</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>76.604.912-5</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9525,13 +9525,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>3517.8</v>
+        <v>3767.53</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1178-37-CM26</t>
+          <t>2467-824-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9556,27 +9556,27 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>Roberto</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>76.604.912-5</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9586,13 +9586,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>46114.6</v>
+        <v>3517.8</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1197-87-CM26</t>
+          <t>1178-37-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9612,32 +9612,32 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9647,13 +9647,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>13993.69</v>
+        <v>46114.6</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1196-151-CM26</t>
+          <t>1197-87-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9688,17 +9688,17 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9708,7 +9708,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>3767.53</v>
+        <v>13993.69</v>
       </c>
     </row>
     <row r="150">
@@ -10901,7 +10901,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1121-73-CM26</t>
+          <t>4732-179-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10921,32 +10921,32 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>69.080.400-K</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>I MUNICIPALIDAD DE CODEGUA</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10956,13 +10956,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>144.24</v>
+        <v>47837.79</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>4732-179-CM26</t>
+          <t>1121-73-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10982,32 +10982,32 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.080.400-K</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CODEGUA</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -11017,7 +11017,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>47837.79</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="171">
@@ -12324,7 +12324,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1134432-566-CM26</t>
+          <t>4451-470-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12349,43 +12349,47 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSPORTES TOGUITA SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
+          <t>77.549.439-5</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>9720.629999999999</v>
+        <v>6031.07</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>4451-470-CM26</t>
+          <t>564953-778-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12410,32 +12414,32 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>TRANSPORTES TOGUITA SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>77.549.439-5</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12444,13 +12448,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>6031.07</v>
+        <v>5594.68</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>564953-778-CM26</t>
+          <t>1134432-566-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12475,47 +12479,43 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Corporación de Educación y Salud de Las Condes</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>5594.68</v>
+        <v>9720.629999999999</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1153624-116-CM26</t>
+          <t>1057439-4946-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12540,27 +12540,27 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>Itravel -  Transporte Privado de Pasajeros</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.935.610-k</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -12570,13 +12570,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>327.07</v>
+        <v>12669.88</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2408-724-CM26</t>
+          <t>1153624-116-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12601,27 +12601,27 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12631,13 +12631,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>14179.41</v>
+        <v>327.07</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3517-127-CM26</t>
+          <t>511077-95-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12657,32 +12657,32 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12692,13 +12692,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>8099.82</v>
+        <v>5049.19</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>675-43-CM26</t>
+          <t>2408-724-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12718,32 +12718,32 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.402.019-9</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12753,13 +12753,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>10942.6</v>
+        <v>14179.41</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1305532-62-CM26</t>
+          <t>3517-127-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12779,32 +12779,32 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>VIVANET</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
+          <t>76.336.696-0</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12814,13 +12814,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>14925.7</v>
+        <v>8099.82</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1658-2266-CM26</t>
+          <t>675-43-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12845,47 +12845,43 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>61.402.019-9</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>TRANSPORTES ALV-BAACK SPA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>77.314.274-2</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>16359.18</v>
+        <v>10942.6</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1057439-4946-CM26</t>
+          <t>1305532-62-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12910,12 +12906,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12925,12 +12921,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Itravel -  Transporte Privado de Pasajeros</t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>76.935.610-k</t>
+          <t>76.018.259-1</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12940,13 +12936,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>12669.88</v>
+        <v>14925.7</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>511077-95-CM26</t>
+          <t>1658-2266-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12966,42 +12962,46 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>TRANSPORTES ALV-BAACK SPA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr"/>
+          <t>77.314.274-2</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>5049.19</v>
+        <v>16359.18</v>
       </c>
     </row>
     <row r="203">
@@ -13068,7 +13068,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1057417-14549-CM26</t>
+          <t>1197-97-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13093,27 +13093,27 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>37143.95</v>
+        <v>15278.84</v>
       </c>
     </row>
     <row r="205">
@@ -13190,7 +13190,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1197-97-CM26</t>
+          <t>1057417-14549-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13215,27 +13215,27 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>15278.84</v>
+        <v>37143.95</v>
       </c>
     </row>
     <row r="207">
@@ -13621,7 +13621,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2792-553-CM26</t>
+          <t>2546-726-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13646,47 +13646,43 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>8.148.859-2</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>29566.36</v>
+        <v>71178.27</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2546-726-CM26</t>
+          <t>1057062-368-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13711,27 +13707,27 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>TRANSPORTES SURAY LIMITADA.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>77.799.670-3</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13741,13 +13737,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>71178.27</v>
+        <v>2354.36</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1057062-368-CM26</t>
+          <t>2792-553-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13772,37 +13768,41 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>TRANSPORTES SURAY LIMITADA.</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>77.799.670-3</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>2354.36</v>
+        <v>29566.36</v>
       </c>
     </row>
     <row r="216">
@@ -13930,7 +13930,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1523-1816-CM26</t>
+          <t>1197-99-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13955,27 +13955,27 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>16.995.419-4</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -13985,13 +13985,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>249028.09</v>
+        <v>27355.86</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>934-134-CM26</t>
+          <t>1523-1816-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14011,52 +14011,48 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>16.995.419-4</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3942.4</v>
+        <v>249028.09</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>4451-503-CM26</t>
+          <t>934-134-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14081,32 +14077,32 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>TRANSPORTES TOGUITA SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>77.549.439-5</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -14115,13 +14111,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>6504.94</v>
+        <v>3942.4</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>4358-167-CM26</t>
+          <t>4451-503-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14146,43 +14142,47 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>TRANSPORTES TOGUITA SPA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr"/>
+          <t>77.549.439-5</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>3821.94</v>
+        <v>6504.94</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1197-99-CM26</t>
+          <t>4358-167-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14202,32 +14202,32 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.170.701-6</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>27355.86</v>
+        <v>3821.94</v>
       </c>
     </row>
     <row r="223">
@@ -14487,7 +14487,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>934-136-CM26</t>
+          <t>934-137-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14527,12 +14527,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>77.659.446-6</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -14546,13 +14546,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>878.41</v>
+        <v>5292.15</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1495208-17-CM26</t>
+          <t>934-136-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14577,32 +14577,32 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.659.446-6</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -14611,13 +14611,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>11707.46</v>
+        <v>878.41</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1495207-11-CM26</t>
+          <t>1495208-17-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14682,7 +14682,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>934-137-CM26</t>
+          <t>1080089-504-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14702,37 +14702,37 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TRANSPORTES, RENT A CAR Y LOGÍSTICA RAMÓN VILLABLANCA BARRIENTOS E.I.R</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>77.551.961-4</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -14741,13 +14741,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>5292.15</v>
+        <v>8458.77</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1080089-504-CM26</t>
+          <t>1385462-131-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14767,37 +14767,37 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>TRANSPORTES, RENT A CAR Y LOGÍSTICA RAMÓN VILLABLANCA BARRIENTOS E.I.R</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>77.551.961-4</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -14806,13 +14806,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>8458.77</v>
+        <v>11707.46</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1385462-131-CM26</t>
+          <t>1495207-11-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -15060,7 +15060,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>3894-78-CM26</t>
+          <t>1260-124-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15080,17 +15080,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15100,12 +15100,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K236" t="inlineStr"/>
@@ -15115,13 +15115,13 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>21782.46</v>
+        <v>26138.95</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1260-124-CM26</t>
+          <t>3894-78-CM26</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15141,17 +15141,17 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15161,12 +15161,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K237" t="inlineStr"/>
@@ -15176,7 +15176,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>26138.95</v>
+        <v>21782.46</v>
       </c>
     </row>
     <row r="238">
@@ -15243,7 +15243,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1198-203-CM26</t>
+          <t>1078634-13-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15268,27 +15268,27 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.402.010-5</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K239" t="inlineStr"/>
@@ -15298,13 +15298,13 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>5193.3</v>
+        <v>43733.05</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1078634-13-CM26</t>
+          <t>1198-203-CM26</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -15329,27 +15329,27 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>61.402.010-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K240" t="inlineStr"/>
@@ -15359,13 +15359,13 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>43733.05</v>
+        <v>5193.3</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2291-1414-CM26</t>
+          <t>1057417-15339-CM26</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -15385,46 +15385,42 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>MARPACIFICO SPA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>77.173.533-9</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>6978.05</v>
+        <v>42076.74</v>
       </c>
     </row>
     <row r="242">
@@ -15556,7 +15552,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1057417-15339-CM26</t>
+          <t>2291-1414-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -15576,48 +15572,52 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>MARPACIFICO SPA</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr"/>
+          <t>77.173.533-9</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>42076.74</v>
+        <v>6978.05</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>932-152-CM26</t>
+          <t>1057539-4659-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15642,43 +15642,47 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>17149.02</v>
+        <v>62192.68</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1057539-4659-CM26</t>
+          <t>967490-77-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15703,47 +15707,43 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>76.310.505-9</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>62192.68</v>
+        <v>11737.55</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>660-24-CM26</t>
+          <t>1057499-443-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -15763,48 +15763,52 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.834.000-7</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Patricio Osvaldo</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>76.845.503-1</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>79190.19</v>
+        <v>20687.7</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>967490-77-CM26</t>
+          <t>1057499-444-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -15824,17 +15828,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15844,28 +15848,32 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>11737.55</v>
+        <v>9472.790000000001</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1057499-443-CM26</t>
+          <t>1057499-445-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -15924,13 +15932,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>20687.7</v>
+        <v>9554.450000000001</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1057499-444-CM26</t>
+          <t>3474-488-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -15950,17 +15958,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -15970,12 +15978,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>78.973.230-2</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -15989,13 +15997,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>9472.790000000001</v>
+        <v>33034.99</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1057499-445-CM26</t>
+          <t>4650-122-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16015,17 +16023,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16035,32 +16043,28 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.621.909-8</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>9554.450000000001</v>
+        <v>272.21</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>3474-488-CM26</t>
+          <t>932-152-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16085,47 +16089,43 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
-        </is>
-      </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.036.979-9</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>33034.99</v>
+        <v>17149.02</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>4650-122-CM26</t>
+          <t>660-24-CM26</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -16150,27 +16150,27 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.834.000-7</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>Patricio Osvaldo</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.845.503-1</t>
         </is>
       </c>
       <c r="K253" t="inlineStr"/>
@@ -16180,7 +16180,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>272.21</v>
+        <v>79190.19</v>
       </c>
     </row>
     <row r="254">
@@ -16308,7 +16308,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1197-107-CM26</t>
+          <t>2793-854-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16328,48 +16328,52 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1452.68</v>
+        <v>36806.65</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1305532-73-CM26</t>
+          <t>1197-107-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16389,32 +16393,32 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>VIVANET</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -16424,13 +16428,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>12914.61</v>
+        <v>1452.68</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2793-854-CM26</t>
+          <t>1305532-73-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16455,47 +16459,43 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.018.259-1</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>36806.65</v>
+        <v>12914.61</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>838794-185-CM26</t>
+          <t>1388961-663-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16515,32 +16515,32 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.980.420-1</t>
+          <t>65.118.035-K</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>SERVICIOS LOGÍSTICOS  Y TRANSPORTES VIÑA DEL MAR SPA</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>76.345.484-3</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -16550,13 +16550,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>6856.65</v>
+        <v>8793.049999999999</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2085-746-CM26</t>
+          <t>838794-185-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16581,27 +16581,27 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.602.226-1</t>
+          <t>61.980.420-1</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>TRANSPORTES KADIMA LIMITADA</t>
+          <t>SERVICIOS LOGÍSTICOS  Y TRANSPORTES VIÑA DEL MAR SPA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>76.336.696-0</t>
+          <t>76.345.484-3</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -16611,13 +16611,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>19927.15</v>
+        <v>6856.65</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1398-1092-CM26</t>
+          <t>1079576-942-CM26</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -16637,37 +16637,37 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>61.954.400-5</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>ABRAHAM PATRICIO VILLANUEVA MICHEA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>15.751.336-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -16676,13 +16676,13 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>8873.370000000001</v>
+        <v>6342.49</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1388961-663-CM26</t>
+          <t>1398-1092-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -16702,48 +16702,52 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>65.118.035-K</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+          <t>ABRAHAM PATRICIO VILLANUEVA MICHEA</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr"/>
+          <t>15.751.336-2</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>8793.049999999999</v>
+        <v>8873.370000000001</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1079576-942-CM26</t>
+          <t>1495199-11-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -16763,22 +16767,22 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>61.954.400-5</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16802,13 +16806,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>6342.49</v>
+        <v>13606.17</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1495199-11-CM26</t>
+          <t>2085-746-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -16833,41 +16837,37 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.602.226-1</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO DE SALUD ARAUCANIA HOSPITAL DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES KADIMA LIMITADA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.336.696-0</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>13606.17</v>
+        <v>19927.15</v>
       </c>
     </row>
     <row r="265">
@@ -16938,7 +16938,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1664-616-CM26</t>
+          <t>1134432-613-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -16963,27 +16963,27 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.602.271-7</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>VIVANET</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K266" t="inlineStr"/>
@@ -16993,13 +16993,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>6287.49</v>
+        <v>2401.43</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>5485-620-CM26</t>
+          <t>5056-3060-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17024,43 +17024,47 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>ABRAHAM PATRICIO VILLANUEVA MICHEA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr"/>
+          <t>15.751.336-2</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>301.09</v>
+        <v>5334.84</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1134432-613-CM26</t>
+          <t>1664-616-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17085,27 +17089,27 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>61.602.271-7</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.018.259-1</t>
         </is>
       </c>
       <c r="K268" t="inlineStr"/>
@@ -17115,13 +17119,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>2401.43</v>
+        <v>6287.49</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>5056-3060-CM26</t>
+          <t>5485-620-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17146,41 +17150,37 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>ABRAHAM PATRICIO VILLANUEVA MICHEA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>15.751.336-2</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>5334.84</v>
+        <v>301.09</v>
       </c>
     </row>
     <row r="270">
@@ -17312,7 +17312,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1422051-306-CM26</t>
+          <t>1057439-5612-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17332,32 +17332,32 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>70.064.202-K</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>EL PUENTE - MAQUINARIA Y CONSTRUCCION SPA</t>
+          <t>Itravel -  Transporte Privado de Pasajeros</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>76.411.861-8</t>
+          <t>76.935.610-k</t>
         </is>
       </c>
       <c r="K272" t="inlineStr"/>
@@ -17367,13 +17367,13 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>40794.03</v>
+        <v>69525.53</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2793-877-CM26</t>
+          <t>1422051-306-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17398,27 +17398,27 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>70.064.202-K</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>JUNTA DE ALCALDES PROVIDENCIA LAS CONDES LA REINA</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>EL PUENTE - MAQUINARIA Y CONSTRUCCION SPA</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.411.861-8</t>
         </is>
       </c>
       <c r="K273" t="inlineStr"/>
@@ -17428,13 +17428,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>15811.97</v>
+        <v>40794.03</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1057439-5612-CM26</t>
+          <t>2793-877-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17454,32 +17454,32 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Itravel -  Transporte Privado de Pasajeros</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>76.935.610-k</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17489,7 +17489,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>69525.53</v>
+        <v>15811.97</v>
       </c>
     </row>
     <row r="275">
@@ -17800,7 +17800,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1079659-376-CM26</t>
+          <t>5485-650-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17820,32 +17820,32 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>LUCANO RENT A CAR S.A.</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>76.813.177-5</t>
         </is>
       </c>
       <c r="K280" t="inlineStr"/>
@@ -17855,13 +17855,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>14866.12</v>
+        <v>97.03</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>5485-650-CM26</t>
+          <t>1079659-376-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -17881,32 +17881,32 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>LUCANO RENT A CAR S.A.</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>76.813.177-5</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K281" t="inlineStr"/>
@@ -17916,13 +17916,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>97.03</v>
+        <v>14866.12</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1199-213-CM26</t>
+          <t>4081-301-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17947,27 +17947,27 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.151.001-8</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>BUSES VILLAR</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>76.465.610-5</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K282" t="inlineStr"/>
@@ -17977,13 +17977,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>38554.16</v>
+        <v>14935.69</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>4081-301-CM26</t>
+          <t>299-168-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18008,27 +18008,27 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>69.151.001-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K283" t="inlineStr"/>
@@ -18038,13 +18038,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>14935.69</v>
+        <v>77200.13</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>299-168-CM26</t>
+          <t>1199-213-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18079,17 +18079,17 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>BUSES VILLAR</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>76.465.610-5</t>
         </is>
       </c>
       <c r="K284" t="inlineStr"/>
@@ -18099,13 +18099,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>77200.13</v>
+        <v>38554.16</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>931-165-CM26</t>
+          <t>5485-657-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18125,32 +18125,32 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K285" t="inlineStr"/>
@@ -18160,13 +18160,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>20647.27</v>
+        <v>300.99</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1134432-647-CM26</t>
+          <t>931-165-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18191,47 +18191,43 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>ALIMENTOS SOL DE QUILLOTA SPA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>77.850.715-3</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.370.023-2</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr"/>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>1440.51</v>
+        <v>20647.27</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>5485-657-CM26</t>
+          <t>1134432-647-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -18251,42 +18247,46 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>ALIMENTOS SOL DE QUILLOTA SPA</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
-        </is>
-      </c>
-      <c r="K287" t="inlineStr"/>
+          <t>77.850.715-3</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>300.99</v>
+        <v>1440.51</v>
       </c>
     </row>
     <row r="288">
@@ -18414,7 +18414,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2427-833-CM26</t>
+          <t>933-70-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -18434,32 +18434,32 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K290" t="inlineStr"/>
@@ -18469,13 +18469,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>7452.57</v>
+        <v>85024.07000000001</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>836-153-CM26</t>
+          <t>2123-317-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -18500,12 +18500,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>72.235.100-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL V REGION</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -18530,13 +18530,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>75458.86</v>
+        <v>10096.61</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1300-294-CM26</t>
+          <t>2427-833-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -18556,22 +18556,22 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>61.961.000-8</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18591,13 +18591,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>637.6799999999999</v>
+        <v>7452.57</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2467-1158-CM26</t>
+          <t>836-153-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -18622,47 +18622,43 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>69.140.900-7</t>
+          <t>72.235.100-2</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILLAN</t>
+          <t>GOBIERNO REGIONAL V REGION</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>INVERSIONES LOF SPA</t>
+          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>77.498.695-2</t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>76.076.244-k</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr"/>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>6450.14</v>
+        <v>75458.86</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2123-317-CM26</t>
+          <t>1300-294-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -18682,32 +18678,32 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>76.076.244-k</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K294" t="inlineStr"/>
@@ -18717,13 +18713,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>10096.61</v>
+        <v>637.6799999999999</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>933-70-CM26</t>
+          <t>2467-1158-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18743,42 +18739,46 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.140.900-7</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>INVERSIONES LOF SPA</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>77.498.695-2</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
           <t>Biobío</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
-        </is>
-      </c>
-      <c r="J295" t="inlineStr">
-        <is>
-          <t>76.470.279-4</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>85024.07000000001</v>
+        <v>6450.14</v>
       </c>
     </row>
     <row r="296">
@@ -18971,7 +18971,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>748-77-CM26</t>
+          <t>748-79-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19011,26 +19011,22 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>ALEMOSO SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>77.852.175-K</t>
-        </is>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>12593.45</v>
+        <v>7309.89</v>
       </c>
     </row>
     <row r="300">
@@ -19158,7 +19154,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>748-79-CM26</t>
+          <t>748-77-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19198,28 +19194,32 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>ALEMOSO SPA</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr"/>
+          <t>77.852.175-K</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>7309.89</v>
+        <v>12593.45</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2735-1056-CM26</t>
+          <t>1059109-94-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19244,47 +19244,43 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.248.427-7</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>55142.84</v>
+        <v>30258.13</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>931-167-CM26</t>
+          <t>2735-1056-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -19304,48 +19300,52 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
-        </is>
-      </c>
-      <c r="K304" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>9912.15</v>
+        <v>55142.84</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1197-122-CM26</t>
+          <t>931-167-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19380,17 +19380,17 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K305" t="inlineStr"/>
@@ -19400,13 +19400,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>8555.75</v>
+        <v>9912.15</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1197-123-CM26</t>
+          <t>1197-122-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>6260.3</v>
+        <v>8555.75</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>813685-229-CM26</t>
+          <t>1197-123-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19492,27 +19492,27 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>LUCANO RENT A CAR S.A.</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>76.813.177-5</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
@@ -19522,13 +19522,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>313.01</v>
+        <v>6260.3</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1059109-94-CM26</t>
+          <t>813685-229-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19548,32 +19548,32 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>LUCANO RENT A CAR S.A.</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.813.177-5</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19583,7 +19583,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>30258.13</v>
+        <v>313.01</v>
       </c>
     </row>
     <row r="309">
@@ -20886,7 +20886,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2427-889-CM26</t>
+          <t>1300-317-SE26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -20906,48 +20906,52 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>76.076.244-k</t>
-        </is>
-      </c>
-      <c r="K330" t="inlineStr"/>
+          <t>78.973.230-2</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>32577.09</v>
+        <v>866.25</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1300-317-SE26</t>
+          <t>2427-889-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -20967,46 +20971,42 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>61.961.000-8</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
-        </is>
-      </c>
-      <c r="K331" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.076.244-k</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>866.25</v>
+        <v>32577.09</v>
       </c>
     </row>
     <row r="332">
@@ -22248,7 +22248,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2123-369-CM26</t>
+          <t>3249-148-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -22273,12 +22273,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.102.049-k</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -22288,12 +22288,12 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K352" t="inlineStr"/>
@@ -22303,13 +22303,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>1737.16</v>
+        <v>2421.8</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>3249-148-CM26</t>
+          <t>2123-369-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -22334,12 +22334,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>61.102.049-k</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -22349,12 +22349,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K353" t="inlineStr"/>
@@ -22364,7 +22364,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>2421.8</v>
+        <v>1737.16</v>
       </c>
     </row>
     <row r="354">
@@ -23114,7 +23114,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>5952-178-CM26</t>
+          <t>934-198-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23139,27 +23139,27 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>ALEJANDRO RAMÓN GONZÁLEZ SILVA</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>7.115.014-3</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K366" t="inlineStr"/>
@@ -23169,13 +23169,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>305.61</v>
+        <v>3565.43</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>5952-179-CM26</t>
+          <t>2547-249-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -23200,27 +23200,27 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>ALEJANDRO RAMÓN GONZÁLEZ SILVA</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>7.115.014-3</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K367" t="inlineStr"/>
@@ -23230,13 +23230,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>203.74</v>
+        <v>6825.24</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2547-249-CM26</t>
+          <t>5952-179-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -23261,27 +23261,27 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>ALEJANDRO RAMÓN GONZÁLEZ SILVA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>7.115.014-3</t>
         </is>
       </c>
       <c r="K368" t="inlineStr"/>
@@ -23291,13 +23291,13 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>6825.24</v>
+        <v>203.74</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>934-198-CM26</t>
+          <t>5952-178-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -23322,27 +23322,27 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>ALEJANDRO RAMÓN GONZÁLEZ SILVA</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>7.115.014-3</t>
         </is>
       </c>
       <c r="K369" t="inlineStr"/>
@@ -23352,13 +23352,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>3565.43</v>
+        <v>305.61</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>5782-48-CM26</t>
+          <t>1300-361-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -23383,12 +23383,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23398,12 +23398,12 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K370" t="inlineStr"/>
@@ -23413,13 +23413,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>813.4400000000001</v>
+        <v>1527.71</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2546-979-CM26</t>
+          <t>5782-48-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -23434,7 +23434,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -23444,27 +23444,27 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K371" t="inlineStr"/>
@@ -23474,13 +23474,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>12284.76</v>
+        <v>813.4400000000001</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2292-7344-CM26</t>
+          <t>1134432-720-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -23495,7 +23495,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -23505,47 +23505,43 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>11670.52</v>
+        <v>510.95</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1274188-749-CM26</t>
+          <t>2546-979-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -23570,27 +23566,27 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>70.934.900-7</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K373" t="inlineStr"/>
@@ -23600,13 +23596,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>30711.9</v>
+        <v>12284.76</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1057539-8780-CM26</t>
+          <t>2292-7344-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -23621,7 +23617,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -23631,43 +23627,47 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>Javier Orlando</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>76.548.886-9</t>
-        </is>
-      </c>
-      <c r="K374" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>58788.95</v>
+        <v>11670.52</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1943-401-CM26</t>
+          <t>1274188-749-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -23682,7 +23682,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -23692,27 +23692,27 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.934.900-7</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K375" t="inlineStr"/>
@@ -23722,71 +23722,193 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>12163.23</v>
+        <v>30711.9</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
+          <t>1057539-8780-CM26</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Javier Orlando</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>76.548.886-9</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="n">
+        <v>58788.95</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>1943-401-CM26</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="n">
+        <v>12163.23</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
           <t>1057417-17061-SE26</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>2239-12-LR25</t>
-        </is>
-      </c>
-      <c r="C376" t="inlineStr">
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr">
+      <c r="D378" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E376" t="inlineStr">
+      <c r="E378" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr">
+      <c r="F378" t="inlineStr">
         <is>
           <t>61.607.301-K</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr">
+      <c r="G378" t="inlineStr">
         <is>
           <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
-      <c r="H376" t="inlineStr">
+      <c r="H378" t="inlineStr">
         <is>
           <t>Biobío</t>
         </is>
       </c>
-      <c r="I376" t="inlineStr">
+      <c r="I378" t="inlineStr">
         <is>
           <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
-      <c r="J376" t="inlineStr">
+      <c r="J378" t="inlineStr">
         <is>
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr">
+      <c r="K378" t="inlineStr">
         <is>
           <t>Araucanía</t>
         </is>
       </c>
-      <c r="L376" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M376" s="2" t="n">
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M378" s="2" t="n">
         <v>314520.87</v>
       </c>
     </row>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/todos.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/todos.xlsx
@@ -20845,7 +20845,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
